--- a/Data/Game/Excel/OdenGameData.xlsx
+++ b/Data/Game/Excel/OdenGameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2240225\Desktop\graphicEngine4\Data\Game\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2BC8B5-94FF-4F21-A1A9-F56768112850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6274F631-37F7-42A7-A8D3-23A3A8B18542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
   </bookViews>
   <sheets>
     <sheet name="OdenGameData" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="39">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1"/>
@@ -178,13 +178,25 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>Egg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tsukune</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Chikuwa</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +208,13 @@
       <sz val="6"/>
       <name val="BIZ UDPゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -221,8 +240,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -559,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3BDE7B-D20C-4439-B65F-69A333B70971}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="12.36328125" customWidth="1"/>
@@ -597,7 +619,7 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -617,7 +639,7 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0.5</v>
@@ -637,7 +659,7 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -657,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -717,7 +739,7 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -737,7 +759,7 @@
         <v>13</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -757,7 +779,7 @@
         <v>13</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0.5</v>
@@ -777,7 +799,7 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0.5</v>
@@ -823,6 +845,366 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0.5</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0.5</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0.5</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0.5</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0.5</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0.5</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0.5</v>
+      </c>
+      <c r="F31">
         <v>0</v>
       </c>
     </row>
@@ -893,10 +1275,10 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -953,10 +1335,10 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
         <v>0</v>

--- a/Data/Game/Excel/OdenGameData.xlsx
+++ b/Data/Game/Excel/OdenGameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2240225\Desktop\graphicEngine4\Data\Game\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6274F631-37F7-42A7-A8D3-23A3A8B18542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD12542E-86BD-4B83-934D-C197AFF23E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
+    <workbookView xWindow="0" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
   </bookViews>
   <sheets>
     <sheet name="OdenGameData" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="45">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1"/>
@@ -190,6 +190,26 @@
   <si>
     <t>Chikuwa</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ingredient</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Egg</t>
+  </si>
+  <si>
+    <t>Konnyaku</t>
+  </si>
+  <si>
+    <t>Chikuwa</t>
+  </si>
+  <si>
+    <t>Tsukune</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C7CF98-D818-4D4E-9B15-9FEDE3940EE8}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.81640625" customWidth="1"/>
@@ -1224,7 +1244,7 @@
     <col min="3" max="3" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1243,8 +1263,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1263,8 +1286,11 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1283,8 +1309,11 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1303,8 +1332,11 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1323,8 +1355,11 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1343,8 +1378,11 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1363,8 +1401,11 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1383,8 +1424,11 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1403,8 +1447,11 @@
       <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1423,8 +1470,11 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1443,8 +1493,11 @@
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1462,6 +1515,9 @@
       </c>
       <c r="F12">
         <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Game/Excel/OdenGameData.xlsx
+++ b/Data/Game/Excel/OdenGameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2240225\Desktop\graphicEngine4\Data\Game\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD12542E-86BD-4B83-934D-C197AFF23E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEC8510-FA58-423B-A457-A38B1BBF346C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
+    <workbookView xWindow="6180" yWindow="675" windowWidth="21600" windowHeight="11295" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
   </bookViews>
   <sheets>
     <sheet name="OdenGameData" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="60">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1"/>
@@ -210,6 +210,66 @@
   </si>
   <si>
     <t>Tsukune</t>
+  </si>
+  <si>
+    <t>UI_Order_RibbonLike</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RibbonLike</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI_Order_Hanpen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI_Order_Goboten</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI_Order_Cake</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI_Order_Donut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI_Order_Shirataki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI_Order_Kobumusubi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hanpen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Goboten</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cake</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Donut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shirataki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kobumusubi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shiraｔaki</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -601,9 +661,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3BDE7B-D20C-4439-B65F-69A333B70971}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" customWidth="1"/>
     <col min="5" max="5" width="14.1796875" customWidth="1"/>
   </cols>
@@ -642,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -662,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -682,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -702,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -762,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -782,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -802,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -822,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1226,6 +1287,726 @@
       </c>
       <c r="F31">
         <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0.5</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0.5</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0.5</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0.5</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A66" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1236,12 +2017,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C7CF98-D818-4D4E-9B15-9FEDE3940EE8}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.81640625" customWidth="1"/>
     <col min="2" max="2" width="15.26953125" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -1384,19 +2166,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1407,30 +2189,30 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
@@ -1448,12 +2230,12 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -1471,12 +2253,12 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
@@ -1494,12 +2276,12 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -1517,7 +2299,168 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Game/Excel/OdenGameData.xlsx
+++ b/Data/Game/Excel/OdenGameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2240225\Desktop\graphicEngine4\Data\Game\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEC8510-FA58-423B-A457-A38B1BBF346C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E09D87-64E5-486C-AD1C-42D86764B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="675" windowWidth="21600" windowHeight="11295" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8EFC4D1F-4C73-4DA9-957D-2C36ACFFB54A}"/>
   </bookViews>
   <sheets>
     <sheet name="OdenGameData" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="61">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1"/>
@@ -269,6 +269,10 @@
   </si>
   <si>
     <t>Shiraｔaki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DonutLike</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1217,7 +1221,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1237,7 +1241,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1977,7 +1981,7 @@
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1997,7 +2001,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2126,7 +2130,7 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <v>1</v>
